--- a/data/trans_dic/IP17-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,56; 25,28</t>
+          <t>13,79; 26,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,45; 33,69</t>
+          <t>18,43; 33,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,79; 32,22</t>
+          <t>17,1; 32,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,19; 33,32</t>
+          <t>16,73; 31,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,08; 32,69</t>
+          <t>17,8; 32,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,39; 31,2</t>
+          <t>16,43; 31,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,5; 31,86</t>
+          <t>17,6; 31,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,9; 21,51</t>
+          <t>10,25; 21,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,36; 26,87</t>
+          <t>17,48; 26,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,37; 30,16</t>
+          <t>19,64; 30,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,4; 29,51</t>
+          <t>18,82; 29,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,46; 24,03</t>
+          <t>14,34; 23,84</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,2; 34,47</t>
+          <t>19,19; 34,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,92; 34,04</t>
+          <t>19,36; 34,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,96; 23,02</t>
+          <t>10,89; 21,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 17,57</t>
+          <t>6,99; 17,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,35; 31,06</t>
+          <t>16,25; 30,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,26; 23,44</t>
+          <t>11,18; 23,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,26; 27,01</t>
+          <t>14,59; 27,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,06; 25,01</t>
+          <t>11,46; 25,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,43; 29,97</t>
+          <t>20,0; 30,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,98; 26,5</t>
+          <t>17,24; 26,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,98; 22,53</t>
+          <t>14,13; 22,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,13; 18,88</t>
+          <t>10,45; 18,83</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,71; 25,83</t>
+          <t>10,54; 25,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,72; 33,35</t>
+          <t>17,1; 32,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,55; 24,39</t>
+          <t>9,45; 24,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 14,26</t>
+          <t>2,46; 14,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,65; 26,79</t>
+          <t>14,3; 28,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,71; 29,47</t>
+          <t>14,73; 30,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 19,83</t>
+          <t>6,63; 20,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,17; 26,31</t>
+          <t>10,13; 26,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,31; 23,87</t>
+          <t>14,12; 23,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,47; 28,32</t>
+          <t>18,73; 29,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,11; 19,43</t>
+          <t>9,77; 19,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,91; 18,16</t>
+          <t>7,82; 18,59</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,78; 24,73</t>
+          <t>15,28; 24,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,61; 27,84</t>
+          <t>18,19; 27,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,49; 27,19</t>
+          <t>18,39; 27,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,89; 18,63</t>
+          <t>8,85; 19,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,81; 29,32</t>
+          <t>19,35; 28,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,59; 30,58</t>
+          <t>20,85; 30,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,77; 25,96</t>
+          <t>16,61; 26,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,52; 23,89</t>
+          <t>14,46; 23,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,11; 25,85</t>
+          <t>19,13; 25,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,16; 27,69</t>
+          <t>21,23; 27,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,84; 25,01</t>
+          <t>19,03; 25,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,82; 19,85</t>
+          <t>12,78; 20,01</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,59; 25,8</t>
+          <t>13,97; 25,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,56; 28,18</t>
+          <t>17,37; 29,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,31; 25,69</t>
+          <t>14,77; 26,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,17; 23,57</t>
+          <t>11,72; 24,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,37; 22,68</t>
+          <t>12,13; 22,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,05; 27,98</t>
+          <t>15,67; 27,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,83; 25,48</t>
+          <t>14,64; 26,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,05; 24,61</t>
+          <t>12,95; 24,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,19; 22,35</t>
+          <t>14,32; 22,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,38; 25,73</t>
+          <t>17,98; 26,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,51; 23,92</t>
+          <t>16,53; 24,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,74; 22,22</t>
+          <t>13,54; 21,94</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,2; 21,13</t>
+          <t>8,42; 21,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,04; 27,49</t>
+          <t>9,98; 27,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,73; 26,79</t>
+          <t>11,43; 28,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,44; 23,04</t>
+          <t>8,25; 21,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,32; 33,43</t>
+          <t>17,48; 33,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,66; 32,41</t>
+          <t>15,03; 32,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 23,61</t>
+          <t>8,96; 24,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,61; 25,73</t>
+          <t>9,45; 25,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,43; 24,44</t>
+          <t>14,56; 25,33</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15,14; 26,92</t>
+          <t>15,25; 26,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,52; 22,76</t>
+          <t>11,84; 22,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,51; 20,44</t>
+          <t>10,06; 20,8</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,07; 22,1</t>
+          <t>17,13; 22,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,93; 26,15</t>
+          <t>20,85; 26,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,6; 22,67</t>
+          <t>17,68; 22,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,17; 17,58</t>
+          <t>12,53; 17,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,92; 24,98</t>
+          <t>19,82; 25,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,85; 25,23</t>
+          <t>20,4; 25,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,4; 22,28</t>
+          <t>17,15; 22,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,03; 20,11</t>
+          <t>15,01; 20,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,11; 22,68</t>
+          <t>19,12; 22,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,25; 24,9</t>
+          <t>20,99; 24,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,16; 21,63</t>
+          <t>18,17; 21,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,55; 18,15</t>
+          <t>14,47; 18,01</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>19862</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22878</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19572</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24773</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>24784</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21098</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23828</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>20538</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>44647</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>43976</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>43401</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>45311</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>14391; 27328</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16577; 30160</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14106; 26731</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17476; 33416</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17367; 31733</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>14745; 28418</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>17443; 30772</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>14036; 30009</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>35299; 54389</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>35297; 54165</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>34167; 52995</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>34618; 57543</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>22955</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24650</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16736</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10491</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19673</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>16068</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>22635</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>16196</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>42628</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>40718</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39371</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>26687</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>16772; 30183</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17924; 31715</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11514; 23122</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6620; 16300</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>13971; 25892</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>10749; 22974</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>16360; 30346</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10948; 23979</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>34667; 52833</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>32545; 50484</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>30775; 49660</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>19883; 35822</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11298</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21023</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9905</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3415</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>20031</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19053</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9220</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>10926</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>31329</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>40076</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>19126</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>14341</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7103; 17129</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14605; 28020</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5844; 14870</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1273; 7276</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>14208; 27914</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>12803; 26249</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5001; 15175</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>6469; 16769</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>23537; 39946</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>32271; 50082</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>13415; 26970</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>9045; 21514</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>39417</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>46925</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>50513</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30202</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>48990</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58655</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>44035</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>41130</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>88407</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>105579</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>94549</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>71332</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>30675; 49850</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>37496; 57547</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>40994; 60367</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>19304; 41801</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>39092; 58412</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>47554; 69188</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>34816; 55491</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>31571; 52026</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>77044; 102095</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>92178; 121403</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>82273; 109685</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>55754; 87293</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>20137</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>33315</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>27279</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>20442</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>21415</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29872</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28133</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>29901</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>41553</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>63187</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>55412</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>50343</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>14540; 26920</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25917; 43355</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20117; 35494</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>14000; 28833</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15437; 28940</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>21844; 38571</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>20754; 36916</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>21054; 39613</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>33148; 52453</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>51869; 75152</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>45957; 66895</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>38197; 61885</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>10415</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9624</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10992</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9356</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>18277</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>16833</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>10482</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>11671</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>28692</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>26457</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>21474</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>6302; 16277</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>5381; 14635</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>6984; 17216</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>5684; 15013</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>12653; 24215</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>11125; 24031</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>6078; 16491</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>6803; 18463</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>21448; 37306</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>19506; 34441</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>15265; 29118</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>14168; 29304</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>124084</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>158414</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>134998</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>98679</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>153171</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>161578</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>138333</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>130362</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>277255</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>319992</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>273331</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>229042</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>109408; 141796</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>141208; 177096</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>118491; 151220</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>82362; 116461</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>135704; 171784</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>145757; 180586</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>121005; 155457</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>112438; 151780</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>253064; 299765</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>292001; 345849</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>250078; 299448</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>203552; 253277</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP17-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,79; 26,19</t>
+          <t>13,63; 26,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,43; 33,54</t>
+          <t>18,33; 33,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,1; 32,41</t>
+          <t>17,34; 31,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,73; 31,99</t>
+          <t>16,77; 32,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,8; 32,53</t>
+          <t>18,49; 32,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,43; 31,66</t>
+          <t>16,78; 31,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,6; 31,06</t>
+          <t>17,54; 31,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 21,92</t>
+          <t>9,98; 20,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,48; 26,94</t>
+          <t>17,47; 27,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,64; 30,14</t>
+          <t>19,11; 29,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,82; 29,19</t>
+          <t>18,56; 29,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,34; 23,84</t>
+          <t>14,64; 24,15</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,19; 34,54</t>
+          <t>18,97; 34,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,36; 34,25</t>
+          <t>19,38; 34,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,89; 21,87</t>
+          <t>10,6; 22,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 17,22</t>
+          <t>6,26; 17,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,25; 30,12</t>
+          <t>15,95; 31,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,18; 23,89</t>
+          <t>11,59; 23,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,59; 27,07</t>
+          <t>13,91; 26,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,46; 25,09</t>
+          <t>11,07; 24,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,0; 30,48</t>
+          <t>19,61; 29,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,24; 26,75</t>
+          <t>17,29; 26,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,13; 22,8</t>
+          <t>14,42; 22,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,45; 18,83</t>
+          <t>10,11; 18,95</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,54; 25,42</t>
+          <t>10,87; 25,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,1; 32,81</t>
+          <t>17,92; 32,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,45; 24,05</t>
+          <t>9,66; 24,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 14,03</t>
+          <t>2,58; 13,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,3; 28,1</t>
+          <t>14,47; 26,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,73; 30,21</t>
+          <t>15,1; 29,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 20,12</t>
+          <t>7,14; 20,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,13; 26,26</t>
+          <t>9,91; 26,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,12; 23,96</t>
+          <t>14,14; 24,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,73; 29,07</t>
+          <t>18,28; 28,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 19,65</t>
+          <t>9,23; 19,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 18,59</t>
+          <t>7,7; 17,86</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,28; 24,83</t>
+          <t>15,63; 24,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,19; 27,92</t>
+          <t>17,99; 27,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,39; 27,08</t>
+          <t>18,17; 27,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 19,17</t>
+          <t>8,75; 18,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,35; 28,91</t>
+          <t>19,47; 29,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,85; 30,33</t>
+          <t>21,45; 30,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,61; 26,48</t>
+          <t>17,0; 25,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,46; 23,84</t>
+          <t>14,4; 24,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,13; 25,35</t>
+          <t>18,81; 25,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,23; 27,96</t>
+          <t>21,14; 27,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,03; 25,36</t>
+          <t>18,88; 25,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,78; 20,01</t>
+          <t>12,69; 19,69</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,97; 25,85</t>
+          <t>13,49; 26,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,37; 29,06</t>
+          <t>16,95; 28,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,77; 26,06</t>
+          <t>14,67; 26,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,72; 24,14</t>
+          <t>11,82; 23,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,13; 22,74</t>
+          <t>12,06; 22,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,67; 27,67</t>
+          <t>16,03; 27,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,64; 26,04</t>
+          <t>14,46; 25,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,95; 24,36</t>
+          <t>12,85; 24,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,32; 22,67</t>
+          <t>14,27; 22,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,98; 26,04</t>
+          <t>17,86; 26,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,53; 24,07</t>
+          <t>16,45; 24,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,54; 21,94</t>
+          <t>13,95; 22,14</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,42; 21,74</t>
+          <t>8,23; 21,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,98; 27,15</t>
+          <t>10,57; 27,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,43; 28,18</t>
+          <t>11,95; 27,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,25; 21,79</t>
+          <t>7,6; 21,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,48; 33,45</t>
+          <t>18,75; 35,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,03; 32,46</t>
+          <t>15,53; 31,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,96; 24,31</t>
+          <t>9,17; 24,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,45; 25,64</t>
+          <t>9,65; 25,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,56; 25,33</t>
+          <t>14,77; 25,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15,25; 26,92</t>
+          <t>15,17; 27,05</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,84; 22,59</t>
+          <t>11,77; 22,64</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,06; 20,8</t>
+          <t>10,4; 20,75</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,13; 22,2</t>
+          <t>16,87; 21,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,85; 26,15</t>
+          <t>21,03; 26,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,68; 22,56</t>
+          <t>17,78; 22,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,53; 17,72</t>
+          <t>12,25; 17,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,82; 25,09</t>
+          <t>19,93; 24,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,4; 25,28</t>
+          <t>20,18; 25,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,15; 22,03</t>
+          <t>17,14; 21,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,01; 20,26</t>
+          <t>14,66; 19,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,12; 22,65</t>
+          <t>19,13; 22,88</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,99; 24,86</t>
+          <t>21,11; 24,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,17; 21,76</t>
+          <t>18,26; 21,48</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,47; 18,01</t>
+          <t>14,52; 18,14</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14391; 27328</t>
+          <t>14218; 27872</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16577; 30160</t>
+          <t>16483; 29970</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14106; 26731</t>
+          <t>14302; 26188</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17476; 33416</t>
+          <t>17517; 33956</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17367; 31733</t>
+          <t>18035; 32073</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14745; 28418</t>
+          <t>15059; 28222</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17443; 30772</t>
+          <t>17377; 31188</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14036; 30009</t>
+          <t>13669; 28232</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35299; 54389</t>
+          <t>35262; 54538</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35297; 54165</t>
+          <t>34339; 53617</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34167; 52995</t>
+          <t>33691; 52734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34618; 57543</t>
+          <t>35345; 58282</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16772; 30183</t>
+          <t>16573; 30432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17924; 31715</t>
+          <t>17945; 31876</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11514; 23122</t>
+          <t>11202; 23873</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6620; 16300</t>
+          <t>5925; 16415</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13971; 25892</t>
+          <t>13708; 27021</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10749; 22974</t>
+          <t>11149; 22131</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16360; 30346</t>
+          <t>15590; 30012</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10948; 23979</t>
+          <t>10577; 23458</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34667; 52833</t>
+          <t>34004; 51809</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32545; 50484</t>
+          <t>32638; 50487</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30775; 49660</t>
+          <t>31403; 49350</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19883; 35822</t>
+          <t>19227; 36046</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7103; 17129</t>
+          <t>7326; 17279</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14605; 28020</t>
+          <t>15303; 28128</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5844; 14870</t>
+          <t>5976; 14992</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1273; 7276</t>
+          <t>1337; 6925</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14208; 27914</t>
+          <t>14376; 26650</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12803; 26249</t>
+          <t>13121; 25979</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5001; 15175</t>
+          <t>5383; 15117</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6469; 16769</t>
+          <t>6330; 17009</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23537; 39946</t>
+          <t>23568; 40389</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32271; 50082</t>
+          <t>31494; 49670</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13415; 26970</t>
+          <t>12665; 26329</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9045; 21514</t>
+          <t>8915; 20662</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30675; 49850</t>
+          <t>31375; 49437</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37496; 57547</t>
+          <t>37077; 56836</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40994; 60367</t>
+          <t>40488; 60201</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19304; 41801</t>
+          <t>19072; 41007</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39092; 58412</t>
+          <t>39352; 58885</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47554; 69188</t>
+          <t>48931; 70621</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34816; 55491</t>
+          <t>35623; 54121</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31571; 52026</t>
+          <t>31431; 52519</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77044; 102095</t>
+          <t>75764; 102642</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>92178; 121403</t>
+          <t>91802; 120016</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82273; 109685</t>
+          <t>81622; 108377</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>55754; 87293</t>
+          <t>55381; 85893</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14540; 26920</t>
+          <t>14043; 27311</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25917; 43355</t>
+          <t>25289; 42331</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20117; 35494</t>
+          <t>19973; 35445</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14000; 28833</t>
+          <t>14121; 28643</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15437; 28940</t>
+          <t>15350; 28476</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21844; 38571</t>
+          <t>22348; 38505</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20754; 36916</t>
+          <t>20506; 36624</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21054; 39613</t>
+          <t>20901; 40511</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33148; 52453</t>
+          <t>33012; 52424</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51869; 75152</t>
+          <t>51540; 75305</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45957; 66895</t>
+          <t>45733; 68162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38197; 61885</t>
+          <t>39357; 62437</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6302; 16277</t>
+          <t>6162; 15755</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5381; 14635</t>
+          <t>5700; 14923</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6984; 17216</t>
+          <t>7298; 16838</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5684; 15013</t>
+          <t>5235; 14693</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12653; 24215</t>
+          <t>13572; 25750</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11125; 24031</t>
+          <t>11500; 23047</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6078; 16491</t>
+          <t>6222; 16909</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6803; 18463</t>
+          <t>6947; 18701</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21448; 37306</t>
+          <t>21748; 37324</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19506; 34441</t>
+          <t>19409; 34609</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15265; 29118</t>
+          <t>15168; 29190</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14168; 29304</t>
+          <t>14657; 29236</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>109408; 141796</t>
+          <t>107802; 140091</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>141208; 177096</t>
+          <t>142388; 176031</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118491; 151220</t>
+          <t>119134; 151050</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>82362; 116461</t>
+          <t>80551; 117266</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>135704; 171784</t>
+          <t>136460; 169129</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>145757; 180586</t>
+          <t>144130; 180956</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>121005; 155457</t>
+          <t>120937; 154749</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>112438; 151780</t>
+          <t>109852; 149438</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>253064; 299765</t>
+          <t>253143; 302756</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>292001; 345849</t>
+          <t>293800; 347601</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>250078; 299448</t>
+          <t>251228; 295490</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>203552; 253277</t>
+          <t>204246; 255160</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP17-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25,41%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24,05%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15,42%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>19,03%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>25,44%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>23,73%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23,71%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>25,41%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,05%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,63; 26,71</t>
+          <t>19,08; 32,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,33; 33,33</t>
+          <t>17,39; 31,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,34; 31,75</t>
+          <t>17,5; 31,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,77; 32,51</t>
+          <t>10,15; 21,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,49; 32,88</t>
+          <t>13,56; 25,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,78; 31,44</t>
+          <t>18,45; 33,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,54; 31,48</t>
+          <t>16,79; 32,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 20,62</t>
+          <t>15,14; 28,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,47; 27,01</t>
+          <t>17,36; 26,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,11; 29,84</t>
+          <t>19,37; 30,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,56; 29,04</t>
+          <t>19,4; 29,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,64; 24,15</t>
+          <t>13,83; 22,63</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16,71%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17,26%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>26,27%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>26,62%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>15,83%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22,88%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>16,71%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,19%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 34,82</t>
+          <t>16,35; 31,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,38; 34,43</t>
+          <t>11,26; 23,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,6; 22,58</t>
+          <t>14,26; 27,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 17,34</t>
+          <t>11,11; 25,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,95; 31,43</t>
+          <t>19,2; 34,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,59; 23,02</t>
+          <t>18,92; 34,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,91; 26,77</t>
+          <t>10,96; 23,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,07; 24,54</t>
+          <t>6,09; 16,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,61; 29,89</t>
+          <t>19,43; 29,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,29; 26,75</t>
+          <t>16,98; 26,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,42; 22,66</t>
+          <t>13,98; 22,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,11; 18,95</t>
+          <t>9,95; 18,5</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,17%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21,93%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17,3%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16,76%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>24,62%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>16,02%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,58%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,17%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,22%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,87; 25,64</t>
+          <t>13,65; 26,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,92; 32,94</t>
+          <t>14,71; 29,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 24,24</t>
+          <t>6,78; 19,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 13,35</t>
+          <t>10,25; 26,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,47; 26,83</t>
+          <t>10,71; 25,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,1; 29,9</t>
+          <t>17,72; 33,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 20,04</t>
+          <t>9,55; 24,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,91; 26,64</t>
+          <t>2,27; 13,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,14; 24,22</t>
+          <t>14,31; 23,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 28,83</t>
+          <t>18,47; 28,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 19,18</t>
+          <t>10,11; 19,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,7; 17,86</t>
+          <t>7,33; 17,37</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24,24%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25,71%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21,01%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18,9%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>19,64%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>22,77%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>22,66%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24,24%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,01%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,63; 24,63</t>
+          <t>19,81; 29,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,99; 27,58</t>
+          <t>20,59; 30,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,17; 27,01</t>
+          <t>16,77; 25,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,75; 18,81</t>
+          <t>14,43; 23,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,47; 29,14</t>
+          <t>15,78; 24,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,45; 30,96</t>
+          <t>18,61; 27,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,0; 25,83</t>
+          <t>18,49; 27,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,4; 24,06</t>
+          <t>12,44; 21,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,81; 25,48</t>
+          <t>19,11; 25,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,14; 27,64</t>
+          <t>21,16; 27,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,88; 25,06</t>
+          <t>18,84; 25,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,69; 19,69</t>
+          <t>14,54; 21,07</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16,82%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19,84%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18,52%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>19,34%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>22,33%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>20,03%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17,12%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>16,82%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>21,43%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,49; 26,23</t>
+          <t>12,37; 22,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,95; 28,38</t>
+          <t>16,05; 27,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,67; 26,03</t>
+          <t>14,83; 25,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,82; 23,98</t>
+          <t>13,02; 25,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,06; 22,37</t>
+          <t>13,59; 25,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,03; 27,63</t>
+          <t>16,56; 28,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 25,83</t>
+          <t>14,31; 25,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,85; 24,91</t>
+          <t>11,88; 23,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,27; 22,65</t>
+          <t>14,19; 22,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,86; 26,1</t>
+          <t>17,38; 25,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,45; 24,52</t>
+          <t>16,51; 23,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,95; 22,14</t>
+          <t>13,61; 22,26</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25,25%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22,74%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15,36%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>13,91%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>17,85%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>17,99%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>25,25%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,45%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,23; 21,04</t>
+          <t>17,32; 33,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,57; 27,68</t>
+          <t>15,66; 32,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,95; 27,56</t>
+          <t>9,29; 23,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,6; 21,33</t>
+          <t>9,09; 24,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,75; 35,57</t>
+          <t>8,2; 21,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,53; 31,13</t>
+          <t>10,04; 27,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,17; 24,93</t>
+          <t>10,73; 26,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,65; 25,97</t>
+          <t>8,39; 23,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,77; 25,34</t>
+          <t>14,43; 24,44</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15,17; 27,05</t>
+          <t>15,14; 26,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,77; 22,64</t>
+          <t>11,52; 22,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,4; 20,75</t>
+          <t>10,32; 20,11</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22,37%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22,62%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19,6%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17,5%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>19,42%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>23,4%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>20,14%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15,01%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>22,37%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,6%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,87; 21,93</t>
+          <t>19,92; 24,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,03; 26,0</t>
+          <t>19,85; 25,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,78; 22,54</t>
+          <t>17,4; 22,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,25; 17,84</t>
+          <t>15,18; 20,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,93; 24,7</t>
+          <t>17,07; 22,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,18; 25,33</t>
+          <t>20,93; 26,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,14; 21,93</t>
+          <t>17,6; 22,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,66; 19,95</t>
+          <t>12,85; 17,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,13; 22,88</t>
+          <t>19,11; 22,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,11; 24,98</t>
+          <t>21,25; 24,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,26; 21,48</t>
+          <t>18,16; 21,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,52; 18,14</t>
+          <t>14,66; 18,26</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24784</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21098</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23828</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18907</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>19862</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>22878</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>19572</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24773</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>24784</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21098</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>23828</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>21706</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45311</t>
+          <t>40613</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14218; 27872</t>
+          <t>18611; 31885</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16483; 29970</t>
+          <t>15608; 28005</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14302; 26188</t>
+          <t>17340; 31571</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17517; 33956</t>
+          <t>12446; 26857</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18035; 32073</t>
+          <t>14148; 26376</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15059; 28222</t>
+          <t>16592; 30297</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17377; 31188</t>
+          <t>13853; 26580</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13669; 28232</t>
+          <t>15586; 29196</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35262; 54538</t>
+          <t>35053; 54253</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34339; 53617</t>
+          <t>34803; 54192</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33691; 52734</t>
+          <t>35224; 53581</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35345; 58282</t>
+          <t>31194; 51033</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19673</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16068</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22635</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15779</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>22955</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>24650</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>16736</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10491</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19673</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16068</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>22635</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26687</t>
+          <t>25991</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16573; 30432</t>
+          <t>14058; 26704</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17945; 31876</t>
+          <t>10824; 22538</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11202; 23873</t>
+          <t>15982; 30277</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5925; 16415</t>
+          <t>10151; 23094</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13708; 27021</t>
+          <t>16780; 30119</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11149; 22131</t>
+          <t>17517; 31519</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15590; 30012</t>
+          <t>11591; 24332</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10577; 23458</t>
+          <t>5880; 16331</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34004; 51809</t>
+          <t>33685; 51962</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32638; 50487</t>
+          <t>32056; 50025</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31403; 49350</t>
+          <t>30442; 49082</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19227; 36046</t>
+          <t>18703; 34778</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>20031</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19053</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9220</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9852</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>11298</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>21023</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>9905</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3415</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>20031</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19053</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9220</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10926</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14341</t>
+          <t>13041</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7326; 17279</t>
+          <t>13559; 26615</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15303; 28128</t>
+          <t>12779; 25610</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5976; 14992</t>
+          <t>5116; 14957</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1337; 6925</t>
+          <t>5834; 15245</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14376; 26650</t>
+          <t>7218; 17405</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13121; 25979</t>
+          <t>15132; 28478</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5383; 15117</t>
+          <t>5909; 15085</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6330; 17009</t>
+          <t>1213; 6998</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23568; 40389</t>
+          <t>23860; 39801</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31494; 49670</t>
+          <t>31824; 48791</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12665; 26329</t>
+          <t>13882; 26676</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8915; 20662</t>
+          <t>8097; 19175</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>48990</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>58655</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44035</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38160</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>39417</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>46925</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>50513</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30202</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>48990</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58655</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>44035</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>29279</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71332</t>
+          <t>67440</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31375; 49437</t>
+          <t>40038; 59256</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37077; 56836</t>
+          <t>46968; 69748</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40488; 60201</t>
+          <t>35150; 54400</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19072; 41007</t>
+          <t>29138; 48423</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39352; 58885</t>
+          <t>31675; 49632</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48931; 70621</t>
+          <t>38355; 57376</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35623; 54121</t>
+          <t>41215; 60602</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31431; 52519</t>
+          <t>22243; 37665</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75764; 102642</t>
+          <t>76985; 104112</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>91802; 120016</t>
+          <t>91888; 120233</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>81622; 108377</t>
+          <t>81462; 108157</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>55381; 85893</t>
+          <t>55363; 80227</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>21415</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>29872</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28133</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>27449</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>20137</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>33315</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>27279</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>20442</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>21415</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29872</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>28133</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29901</t>
+          <t>19916</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50343</t>
+          <t>47365</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14043; 27311</t>
+          <t>15746; 28869</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25289; 42331</t>
+          <t>22367; 39004</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19973; 35445</t>
+          <t>21030; 36117</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14121; 28643</t>
+          <t>19302; 37269</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15350; 28476</t>
+          <t>14145; 26865</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22348; 38505</t>
+          <t>24708; 42032</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20506; 36624</t>
+          <t>19487; 34990</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20901; 40511</t>
+          <t>14109; 27310</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33012; 52424</t>
+          <t>32845; 51726</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51540; 75305</t>
+          <t>50164; 74236</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45733; 68162</t>
+          <t>45895; 66493</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>39357; 62437</t>
+          <t>36346; 59438</t>
         </is>
       </c>
     </row>
@@ -2831,37 +2831,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>18277</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>16833</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10482</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10491</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>10415</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>9624</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>10992</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9356</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>18277</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>16833</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>10482</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21028</t>
+          <t>20077</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6162; 15755</t>
+          <t>12538; 24201</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5700; 14923</t>
+          <t>11593; 23997</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7298; 16838</t>
+          <t>6298; 16010</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5235; 14693</t>
+          <t>6210; 16747</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13572; 25750</t>
+          <t>6139; 15821</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11500; 23047</t>
+          <t>5415; 14818</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6222; 16909</t>
+          <t>6554; 16365</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6947; 18701</t>
+          <t>5899; 16401</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21748; 37324</t>
+          <t>21245; 35985</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19409; 34609</t>
+          <t>19372; 34443</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15168; 29190</t>
+          <t>14855; 29346</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14657; 29236</t>
+          <t>14308; 27878</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>228</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>151</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>153171</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>161578</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>138333</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>120638</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>124084</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>158414</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>134998</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>98679</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>153171</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>161578</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>138333</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>130362</t>
+          <t>93889</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>229042</t>
+          <t>214526</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>107802; 140091</t>
+          <t>136343; 170982</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>142388; 176031</t>
+          <t>141777; 180239</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119134; 151050</t>
+          <t>122794; 157257</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>80551; 117266</t>
+          <t>104656; 140753</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>136460; 169129</t>
+          <t>109063; 141158</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>144130; 180956</t>
+          <t>141738; 177056</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>120937; 154749</t>
+          <t>117982; 151921</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>109852; 149438</t>
+          <t>79806; 107912</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>253143; 302756</t>
+          <t>252942; 300224</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>293800; 347601</t>
+          <t>295664; 346511</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>251228; 295490</t>
+          <t>249805; 297680</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>204246; 255160</t>
+          <t>192112; 239251</t>
         </is>
       </c>
     </row>
